--- a/src/clients/ApplicationTracker.React/public/templates/ApplicationRecords_Import_Template.xlsx
+++ b/src/clients/ApplicationTracker.React/public/templates/ApplicationRecords_Import_Template.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\FullStackProject\ApplicationTracker\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\FullStackProject\ApplicationTracker\src\clients\ApplicationTracker.React\public\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4757DF04-0071-4484-BCFF-F44E88A8D0F1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8E36417-DA53-4185-8FB1-4104ACBE24A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3690" yWindow="5085" windowWidth="28800" windowHeight="15435" xr2:uid="{0DC61EF3-0AB4-4D72-BBD1-F2775F03C231}"/>
+    <workbookView xWindow="-38520" yWindow="-60" windowWidth="38640" windowHeight="21240" xr2:uid="{0DC61EF3-0AB4-4D72-BBD1-F2775F03C231}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -421,7 +421,7 @@
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D1" t="s">

--- a/src/clients/ApplicationTracker.React/public/templates/ApplicationRecords_Import_Template.xlsx
+++ b/src/clients/ApplicationTracker.React/public/templates/ApplicationRecords_Import_Template.xlsx
@@ -1,81 +1,118 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
-  <workbookPr defaultThemeVersion="166925"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\FullStackProject\ApplicationTracker\src\clients\ApplicationTracker.React\public\templates\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8E36417-DA53-4185-8FB1-4104ACBE24A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-60" windowWidth="38640" windowHeight="21240" xr2:uid="{0DC61EF3-0AB4-4D72-BBD1-F2775F03C231}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-38520" yWindow="-60" windowWidth="38640" windowHeight="21240" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Instructions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Data" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="181029"/>
-  <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="181029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
-  <si>
-    <t>CompanyName</t>
-  </si>
-  <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t>AppliedDate</t>
-  </si>
-  <si>
-    <t>PostingUrl</t>
-  </si>
-  <si>
-    <t>Notes</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="10">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <color rgb="001F4E79"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00C00000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <color rgb="00375623"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <color rgb="00595959"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="9">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="1" tint="0.34998626667073579"/>
+        <fgColor theme="1" tint="0.3499862666707358"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001F4E79"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00DEEAF1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002E75B6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00365F91"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -83,27 +120,145 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00BFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="00BFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="00BFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00BFBFBF"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+  <cellXfs count="17">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -403,32 +558,488 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CD80AB12-93D0-41AE-B1AC-2189755EE6B2}">
-  <dimension ref="A1:E1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E28"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="14.7109375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="6.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="38" customWidth="1" min="3" max="3"/>
+    <col width="40" customWidth="1" min="4" max="4"/>
+    <col width="32" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="2" t="inlineStr">
+        <is>
+          <t>ApplicationTracker — Import Template Instructions</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>Use the Data sheet to enter your applications. Do not modify the header row on the Data sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="8" customHeight="1"/>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Column Guide</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="18" customHeight="1">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>Column</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>Required?</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Format / Accepted Values</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>Example</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>CompanyName (A)</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>Any text</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>Name of the company you applied to</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>Status (B)</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C7" s="8" t="inlineStr">
+        <is>
+          <t>Applied / Interviewing / Offered / Rejected / Withdrawn</t>
+        </is>
+      </c>
+      <c r="D7" s="8" t="inlineStr">
+        <is>
+          <t>Interviewing</t>
+        </is>
+      </c>
+      <c r="E7" s="8" t="inlineStr">
+        <is>
+          <t>Text name only — do NOT use numbers. Case-insensitive.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>AppliedDate (C)</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>YYYY-MM-DD  (e.g. 2026-06-17)</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="inlineStr">
+        <is>
+          <t>2026-06-01</t>
+        </is>
+      </c>
+      <c r="E8" s="6" t="inlineStr">
+        <is>
+          <t>Future dates are rejected. Leave no time component.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>PostingUrl (D)</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C9" s="8" t="inlineStr">
+        <is>
+          <t>Full URL starting with http:// or https://</t>
+        </is>
+      </c>
+      <c r="D9" s="8" t="inlineStr">
+        <is>
+          <t>https://careers.google.com/jobs/123</t>
+        </is>
+      </c>
+      <c r="E9" s="8" t="inlineStr">
+        <is>
+          <t>Leave blank if no posting URL available</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="18" customHeight="1">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>Notes (E)</t>
+        </is>
+      </c>
+      <c r="B10" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="C10" s="6" t="inlineStr">
+        <is>
+          <t>Any text</t>
+        </is>
+      </c>
+      <c r="D10" s="6" t="inlineStr">
+        <is>
+          <t>Referred by a contact</t>
+        </is>
+      </c>
+      <c r="E10" s="6" t="inlineStr">
+        <is>
+          <t>Free-form; leave blank if none</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="8" customHeight="1"/>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>Rules and Validation</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="18" customHeight="1">
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t>• CompanyName and AppliedDate are required for every row — rows missing either will be skipped with an error.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="18" customHeight="1">
+      <c r="A14" s="13" t="inlineStr">
+        <is>
+          <t>• Status must be the text name (Applied, Interviewing, Offered, Rejected, Withdrawn). Numeric values (0–4) are rejected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="18" customHeight="1">
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>• Duplicate detection: if a record with the same CompanyName + PostingUrl already exists in your account it will be skipped.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="18" customHeight="1">
+      <c r="A16" s="13" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  If no PostingUrl is provided, CompanyName + AppliedDate is used for duplicate detection instead.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="18" customHeight="1">
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>• PostingUrl must be a valid http:// or https:// URL if provided. Partial URLs (e.g. "careers.google.com") will be rejected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="18" customHeight="1">
+      <c r="A18" s="13" t="inlineStr">
+        <is>
+          <t>• Future dates are not accepted for AppliedDate.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="18" customHeight="1">
+      <c r="A19" s="12" t="inlineStr">
+        <is>
+          <t>• Extra columns beyond column E are ignored.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="13" t="inlineStr">
+        <is>
+          <t>• Do not modify or delete the header row (row 1) on the Data sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="8" customHeight="1"/>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>Example Rows (for reference only — do not paste into the Data sheet)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="18" customHeight="1">
+      <c r="A23" s="14" t="inlineStr">
+        <is>
+          <t>CompanyName</t>
+        </is>
+      </c>
+      <c r="B23" s="14" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="C23" s="14" t="inlineStr">
+        <is>
+          <t>AppliedDate</t>
+        </is>
+      </c>
+      <c r="D23" s="14" t="inlineStr">
+        <is>
+          <t>PostingUrl</t>
+        </is>
+      </c>
+      <c r="E23" s="14" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="16" customHeight="1">
+      <c r="A24" s="15" t="inlineStr">
+        <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="B24" s="15" t="inlineStr">
+        <is>
+          <t>Applied</t>
+        </is>
+      </c>
+      <c r="C24" s="15" t="inlineStr">
+        <is>
+          <t>2026-06-15</t>
+        </is>
+      </c>
+      <c r="D24" s="15" t="inlineStr">
+        <is>
+          <t>https://careers.google.com/jobs/123</t>
+        </is>
+      </c>
+      <c r="E24" s="15" t="inlineStr"/>
+    </row>
+    <row r="25" ht="16" customHeight="1">
+      <c r="A25" s="16" t="inlineStr">
+        <is>
+          <t>Microsoft</t>
+        </is>
+      </c>
+      <c r="B25" s="16" t="inlineStr">
+        <is>
+          <t>Interviewing</t>
+        </is>
+      </c>
+      <c r="C25" s="16" t="inlineStr">
+        <is>
+          <t>2026-05-20</t>
+        </is>
+      </c>
+      <c r="D25" s="16" t="inlineStr">
+        <is>
+          <t>https://careers.microsoft.com/job/456</t>
+        </is>
+      </c>
+      <c r="E25" s="16" t="inlineStr">
+        <is>
+          <t>Phone screen passed</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="16" customHeight="1">
+      <c r="A26" s="15" t="inlineStr">
+        <is>
+          <t>Airbnb</t>
+        </is>
+      </c>
+      <c r="B26" s="15" t="inlineStr">
+        <is>
+          <t>Offered</t>
+        </is>
+      </c>
+      <c r="C26" s="15" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="D26" s="15" t="inlineStr"/>
+      <c r="E26" s="15" t="inlineStr">
+        <is>
+          <t>Offer expires June 30</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="16" customHeight="1">
+      <c r="A27" s="16" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="B27" s="16" t="inlineStr">
+        <is>
+          <t>Rejected</t>
+        </is>
+      </c>
+      <c r="C27" s="16" t="inlineStr">
+        <is>
+          <t>2026-03-01</t>
+        </is>
+      </c>
+      <c r="D27" s="16" t="inlineStr">
+        <is>
+          <t>https://amazon.jobs/en/jobs/789</t>
+        </is>
+      </c>
+      <c r="E27" s="16" t="inlineStr">
+        <is>
+          <t>Did not pass bar raiser</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="16" customHeight="1">
+      <c r="A28" s="15" t="inlineStr">
+        <is>
+          <t>Startup Co</t>
+        </is>
+      </c>
+      <c r="B28" s="15" t="inlineStr">
+        <is>
+          <t>Withdrawn</t>
+        </is>
+      </c>
+      <c r="C28" s="15" t="inlineStr">
+        <is>
+          <t>2026-02-14</t>
+        </is>
+      </c>
+      <c r="D28" s="15" t="inlineStr"/>
+      <c r="E28" s="15" t="inlineStr">
+        <is>
+          <t>Accepted a different offer</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A12:E12"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="A20:E20"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A16:E16"/>
+    <mergeCell ref="A15:E15"/>
+    <mergeCell ref="A19:E19"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A13:E13"/>
+    <mergeCell ref="A14:E14"/>
+    <mergeCell ref="A22:E22"/>
+    <mergeCell ref="A17:E17"/>
+    <mergeCell ref="A18:E18"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14.7109375" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="6.42578125" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="12.140625" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="10.140625" bestFit="1" customWidth="1" min="4" max="4"/>
+    <col width="6.28515625" bestFit="1" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>CompanyName</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>AppliedDate</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>PostingUrl</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/src/clients/ApplicationTracker.React/public/templates/ApplicationRecords_Import_Template.xlsx
+++ b/src/clients/ApplicationTracker.React/public/templates/ApplicationRecords_Import_Template.xlsx
@@ -676,7 +676,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="30" customHeight="1">
+    <row r="8" ht="60" customHeight="1">
       <c r="A8" s="6" t="inlineStr">
         <is>
           <t>AppliedDate (C)</t>
@@ -689,17 +689,20 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>YYYY-MM-DD  (e.g. 2026-06-17)</t>
+          <t>YYYY-MM-DD (recommended)
+MM/DD/YYYY
+YYYY/MM/DD
+MMM D, YYYY (e.g. Jun 18, 2026)</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>2026-06-01</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>Future dates are rejected. Leave no time component.</t>
+          <t>Multiple formats accepted; YYYY-MM-DD is least ambiguous. Future dates are rejected.</t>
         </is>
       </c>
     </row>
